--- a/output/quickfixclose10_portfolio_daily.xlsx
+++ b/output/quickfixclose10_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150,641.62</t>
+          <t>149,102.76</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+50.64%</t>
+          <t>+49.10%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>155,924  (+55.92%)</t>
+          <t>154,503  (+54.50%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,610  (5.3 pts of return)</t>
+          <t>3,775  (5.4 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.5x</t>
+          <t>2.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,218  (-1.26%)</t>
+          <t>-1,225  (-1.26%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5747,22 +5747,74 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>150641.62</v>
+        <v>150775.69</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>-0</v>
+        <v>5579.74</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>150641.62</v>
+        <v>145195.95</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX exit_close (+7,827); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>Gold_Futures_COMEX exit_close (+7,827)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>150775.69</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>5579.74</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>145195.95</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>149102.76</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>149102.76</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,594); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9834,7 @@
         <v>11626.79</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>166643.64</v>
+        <v>166736.27</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9825,7 +9877,7 @@
         <v>-40.16</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>155069.32</v>
+        <v>166696.11</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9868,7 +9920,7 @@
         <v>-52.47</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>155016.86</v>
+        <v>166643.64</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9911,7 +9963,7 @@
         <v>-25.87</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>166536.15</v>
+        <v>164250.52</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9935,14 +9987,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>146815.3</v>
@@ -9951,14 +10011,14 @@
         <v>2040.73</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>-81.63</v>
+        <v>-2367.25</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>166562.01</v>
+        <v>164276.39</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose10_portfolio_daily.xlsx
+++ b/output/quickfixclose10_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>149,102.76</t>
+          <t>149,094.95</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+49.10%</t>
+          <t>+49.09%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,775  (5.4 pts of return)</t>
+          <t>3,783  (5.4 pts of return)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>83% of trading days</t>
+          <t>84% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5799,22 +5799,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>149102.76</v>
+        <v>149181.88</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>-0</v>
+        <v>4205.76</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>149102.76</v>
+        <v>144976.11</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,594); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-1,594)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>149181.88</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>8511.700000000001</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>140670.18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 1,450); Nasdaq_100_E_mini short (risk 1,435); S_P_500_E_mini short (risk 1,421)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>149094.95</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>149094.95</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,407)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9877,7 +9937,7 @@
         <v>-40.16</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>166696.11</v>
+        <v>164328.86</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9920,7 +9980,7 @@
         <v>-52.47</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>166643.64</v>
+        <v>164276.39</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9963,7 +10023,7 @@
         <v>-25.87</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>164250.52</v>
+        <v>164238.72</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -10014,11 +10074,183 @@
         <v>-2367.25</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>164276.39</v>
+        <v>164369.02</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>158072.59</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2197.21</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>164265.04</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>155875.38</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2166.67</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>164272.67</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>153708.72</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>2136.55</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>164264.59</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>151572.17</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>2106.85</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>164272.79</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose10_portfolio_daily.xlsx
+++ b/output/quickfixclose10_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>149,094.95</t>
+          <t>174,497.83</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+49.09%</t>
+          <t>+74.50%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>154,503  (+54.50%)</t>
+          <t>180,850  (+80.85%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,783  (5.4 pts of return)</t>
+          <t>3,861  (6.4 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.4x</t>
+          <t>3.6x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.5 bars</t>
+          <t>4.6 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6.73R  (best +15.35R)</t>
+          <t>+6.99R  (best +15.35R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,392  (+6.73%)</t>
+          <t>7,057  (+6.99%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,225  (-1.26%)</t>
+          <t>-1,228  (-1.25%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5855,26 +5855,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>149094.95</v>
+        <v>149181.88</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>9918.4</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>139263.47</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,407)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>174497.83</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>149094.95</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>174497.83</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 1,407)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 1,393); NY_Palladium_Futures short (risk 1,379)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT exit_close (+17,687); Corn_CBOT_Futures exit_close (+9,077); Gold_Futures_COMEX stop (-1,416); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9918,14 +9946,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>12.528</v>
       </c>
       <c r="G79" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.019</v>
+        <v>12.491</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>153111.72</v>
@@ -9933,15 +9969,15 @@
       <c r="J79" s="5" t="n">
         <v>2128.25</v>
       </c>
-      <c r="K79" s="6" t="n">
-        <v>-40.16</v>
+      <c r="K79" s="7" t="n">
+        <v>26583.08</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>164328.86</v>
+        <v>190952.1</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9961,14 +9997,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>10</v>
+      </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>6.525</v>
       </c>
       <c r="G80" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.025</v>
+        <v>6.475</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>150983.47</v>
@@ -9976,15 +10020,15 @@
       <c r="J80" s="5" t="n">
         <v>2098.67</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>-52.47</v>
+      <c r="K80" s="7" t="n">
+        <v>13588.89</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>164276.39</v>
+        <v>204540.99</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10067,7 @@
         <v>-25.87</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>164238.72</v>
+        <v>202372.01</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -10117,7 +10161,7 @@
         <v>-7.63</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>164265.04</v>
+        <v>202398.33</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10160,7 +10204,7 @@
         <v>-0.12</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>164272.67</v>
+        <v>202419.61</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10203,7 +10247,7 @@
         <v>-0.45</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>164264.59</v>
+        <v>202397.88</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10227,14 +10271,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>151572.17</v>
@@ -10243,12 +10295,98 @@
         <v>2106.85</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>-3.6</v>
+        <v>-2121.26</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>164272.79</v>
+        <v>202419.73</v>
       </c>
       <c r="M86" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>149465.31</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>2077.57</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>202413.99</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>147387.74</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>2048.69</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>202405.96</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
